--- a/product family/MXDASH/MXDASH 15+1 RCPT (218342)/BOM.xlsx
+++ b/product family/MXDASH/MXDASH 15+1 RCPT (218342)/BOM.xlsx
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>2183429001</v>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>2183429001</v>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
         <v>2183429001</v>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
         <v>2183429001</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
         <v>2183429001</v>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
         <v>2183429001</v>
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>2183429002</v>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>2183429002</v>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>2183429002</v>
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
         <v>2183429002</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
         <v>2183429002</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
         <v>2183429002</v>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
         <v>2183429002</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>2183429003</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>2183429003</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
         <v>2183429003</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
         <v>2183429003</v>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
         <v>2183429003</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
         <v>2183429003</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H22" t="n">
         <v>2183429003</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
         <v>2183429004</v>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
         <v>2183429004</v>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
         <v>2183429004</v>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
         <v>2183429004</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
         <v>2183429004</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H28" t="n">
         <v>2183429004</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H29" t="n">
         <v>2183429004</v>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
         <v>2183429013</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
         <v>2183429013</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
         <v>2183429013</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H34" t="n">
         <v>2183429013</v>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H35" t="n">
         <v>2183429013</v>
@@ -1742,12 +1742,8 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
-        <v>7</v>
-      </c>
-      <c r="G36" t="n">
-        <v>7</v>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2183429013</v>
       </c>
@@ -1779,10 +1775,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>2183429014</v>
@@ -1815,10 +1811,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
         <v>2183429014</v>
@@ -1851,10 +1847,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H39" t="n">
         <v>2183429014</v>
@@ -1887,10 +1883,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H40" t="n">
         <v>2183429014</v>
@@ -1923,10 +1919,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H41" t="n">
         <v>2183429014</v>
@@ -1959,10 +1955,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H42" t="n">
         <v>2183429014</v>
@@ -1982,12 +1978,8 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>7</v>
-      </c>
-      <c r="G43" t="n">
-        <v>7</v>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2183429014</v>
       </c>
@@ -2019,10 +2011,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
         <v>2183429015</v>
@@ -2055,10 +2047,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
         <v>2183429015</v>
@@ -2091,10 +2083,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
         <v>2183429015</v>
@@ -2127,10 +2119,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H47" t="n">
         <v>2183429015</v>
@@ -2163,10 +2155,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H48" t="n">
         <v>2183429015</v>
@@ -2199,10 +2191,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
         <v>2183429015</v>
@@ -2222,12 +2214,8 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="n">
-        <v>7</v>
-      </c>
-      <c r="G50" t="n">
-        <v>7</v>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2183429015</v>
       </c>
@@ -2259,10 +2247,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
         <v>2183429016</v>
@@ -2295,10 +2283,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H52" t="n">
         <v>2183429016</v>
@@ -2331,10 +2319,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
         <v>2183429016</v>
@@ -2367,10 +2355,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H54" t="n">
         <v>2183429016</v>
@@ -2403,10 +2391,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G55" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H55" t="n">
         <v>2183429016</v>
@@ -2439,10 +2427,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H56" t="n">
         <v>2183429016</v>
@@ -2462,12 +2450,8 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="n">
-        <v>7</v>
-      </c>
-      <c r="G57" t="n">
-        <v>7</v>
-      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>2183429016</v>
       </c>
